--- a/34th_Backgammon-championships_3b_output.xlsx
+++ b/34th_Backgammon-championships_3b_output.xlsx
@@ -861,11 +861,6 @@
           <t>5171653</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>5171454</t>
-        </is>
-      </c>
       <c r="F9" s="1" t="inlineStr">
         <is>
           <t>5171601</t>
@@ -1054,28 +1049,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1102,7 +1096,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -1187,13 +1181,13 @@
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
         <v>9</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
         <v>7</v>
@@ -1224,7 +1218,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1352,7 +1346,7 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="n">
         <v>7</v>
@@ -1407,7 +1401,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -1437,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P9" t="n">
         <v>11</v>
@@ -1446,7 +1440,7 @@
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1537,12 +1531,6 @@
       <c r="G11" t="n">
         <v>11</v>
       </c>
-      <c r="H11" t="n">
-        <v>11</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6</v>
-      </c>
       <c r="J11" t="n">
         <v>8</v>
       </c>
@@ -1575,7 +1563,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>

--- a/34th_Backgammon-championships_3b_output.xlsx
+++ b/34th_Backgammon-championships_3b_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Links" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Matches" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Players" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Control" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matches" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Players" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -673,19 +673,9 @@
           <t>5171187</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>5171292</t>
-        </is>
-      </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
           <t>5171221</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>5171189</t>
         </is>
       </c>
     </row>
@@ -1017,59 +1007,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K5" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1085,13 +1073,74 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2"/>
-    <row r="3"/>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>averell</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>beyazit</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ELANRA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>gleneagle59</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>itcfbod</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mandria</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Otis</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SGE2019</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>tochev71</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uli1001</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>averell</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
@@ -1117,16 +1166,16 @@
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
         <v>5</v>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
         <v>11</v>
@@ -1159,6 +1208,16 @@
       <c r="C5" t="n">
         <v>6</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
@@ -1184,10 +1243,10 @@
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P5" t="n">
         <v>7</v>
@@ -1218,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -1226,6 +1285,16 @@
       <c r="E6" t="n">
         <v>11</v>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
@@ -1242,7 +1311,7 @@
         <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
@@ -1293,6 +1362,16 @@
       <c r="G7" t="n">
         <v>10</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="J7" t="n">
         <v>10</v>
       </c>
@@ -1311,24 +1390,12 @@
       <c r="O7" t="n">
         <v>11</v>
       </c>
-      <c r="P7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>10</v>
-      </c>
       <c r="R7" t="n">
         <v>8</v>
       </c>
       <c r="S7" t="n">
         <v>11</v>
       </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>6</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1360,6 +1427,16 @@
       <c r="I8" t="n">
         <v>10</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L8" t="n">
         <v>11</v>
       </c>
@@ -1401,7 +1478,7 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -1410,7 +1487,7 @@
         <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
         <v>10</v>
@@ -1427,6 +1504,16 @@
       <c r="K9" t="n">
         <v>11</v>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="N9" t="n">
         <v>10</v>
       </c>
@@ -1440,7 +1527,7 @@
         <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1488,6 +1575,16 @@
       <c r="M10" t="n">
         <v>5</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="P10" t="n">
         <v>7</v>
       </c>
@@ -1549,6 +1646,16 @@
       <c r="O11" t="n">
         <v>7</v>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="R11" t="n">
         <v>10</v>
       </c>
@@ -1563,7 +1670,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
@@ -1596,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N12" t="n">
         <v>4</v>
@@ -1610,6 +1717,16 @@
       <c r="Q12" t="n">
         <v>10</v>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T12" t="n">
         <v>6</v>
       </c>
@@ -1671,9 +1788,31 @@
       <c r="S13" t="n">
         <v>11</v>
       </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14"/>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="H3:I3"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
@@ -1802,13 +1941,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>MATCH_IDS_FILLED</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
